--- a/Schedule Templates (1).xlsx
+++ b/Schedule Templates (1).xlsx
@@ -3,7 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="5P-3R-2T Standard" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="7P-4R-3T Standard" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="6P-3R-3T Standard" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="6P-4R-2T Standard" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="8P-4R-4T Standard" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="4P-2R-2T Standard" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="3P-2R-1T Standard" sheetId="7" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="19">
   <si>
     <t xml:space="preserve">Pilots </t>
   </si>
@@ -51,6 +57,24 @@
   <si>
     <t>Task 2</t>
   </si>
+  <si>
+    <t>Pilot 6</t>
+  </si>
+  <si>
+    <t>Pilot 7</t>
+  </si>
+  <si>
+    <t>Robot 4</t>
+  </si>
+  <si>
+    <t>Task 3</t>
+  </si>
+  <si>
+    <t>Pilot 8</t>
+  </si>
+  <si>
+    <t>Task 4</t>
+  </si>
 </sst>
 </file>
 
@@ -73,7 +97,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -110,6 +134,24 @@
         <bgColor rgb="FF46BDC6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF6D01"/>
+        <bgColor rgb="FFFF6D01"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8649B3"/>
+        <bgColor rgb="FF8649B3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF10E02C"/>
+        <bgColor rgb="FF10E02C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border/>
@@ -117,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -145,6 +187,15 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -154,6 +205,30 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -667,4 +742,2688 @@
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8.38"/>
+    <col customWidth="1" min="2" max="37" width="5.75"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="E1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2"/>
+      <c r="E2" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="7"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="4"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="5"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="6"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="9"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="10"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="10"/>
+      <c r="T12" s="10"/>
+      <c r="U12" s="10"/>
+      <c r="V12" s="10"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="5"/>
+      <c r="Y12" s="5"/>
+      <c r="Z12" s="5"/>
+      <c r="AA12" s="7"/>
+      <c r="AB12" s="7"/>
+      <c r="AC12" s="7"/>
+      <c r="AD12" s="7"/>
+      <c r="AE12" s="6"/>
+      <c r="AF12" s="6"/>
+      <c r="AG12" s="6"/>
+      <c r="AH12" s="6"/>
+      <c r="AI12" s="3"/>
+      <c r="AJ12" s="3"/>
+      <c r="AK12" s="3"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7"/>
+      <c r="X13" s="6"/>
+      <c r="Y13" s="6"/>
+      <c r="Z13" s="6"/>
+      <c r="AA13" s="6"/>
+      <c r="AB13" s="3"/>
+      <c r="AC13" s="3"/>
+      <c r="AD13" s="3"/>
+      <c r="AE13" s="3"/>
+      <c r="AF13" s="9"/>
+      <c r="AG13" s="9"/>
+      <c r="AH13" s="9"/>
+      <c r="AI13" s="9"/>
+      <c r="AJ13" s="4"/>
+      <c r="AK13" s="4"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
+      <c r="T14" s="6"/>
+      <c r="U14" s="3"/>
+      <c r="V14" s="3"/>
+      <c r="W14" s="3"/>
+      <c r="X14" s="3"/>
+      <c r="Y14" s="9"/>
+      <c r="Z14" s="9"/>
+      <c r="AA14" s="9"/>
+      <c r="AB14" s="9"/>
+      <c r="AC14" s="4"/>
+      <c r="AD14" s="4"/>
+      <c r="AE14" s="4"/>
+      <c r="AF14" s="4"/>
+      <c r="AG14" s="10"/>
+      <c r="AH14" s="10"/>
+      <c r="AI14" s="10"/>
+      <c r="AJ14" s="10"/>
+      <c r="AK14" s="5"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="9"/>
+      <c r="S15" s="9"/>
+      <c r="T15" s="9"/>
+      <c r="U15" s="9"/>
+      <c r="V15" s="4"/>
+      <c r="W15" s="4"/>
+      <c r="X15" s="4"/>
+      <c r="Y15" s="4"/>
+      <c r="Z15" s="10"/>
+      <c r="AA15" s="10"/>
+      <c r="AB15" s="10"/>
+      <c r="AC15" s="10"/>
+      <c r="AD15" s="5"/>
+      <c r="AE15" s="5"/>
+      <c r="AF15" s="5"/>
+      <c r="AG15" s="5"/>
+      <c r="AH15" s="7"/>
+      <c r="AI15" s="7"/>
+      <c r="AJ15" s="7"/>
+      <c r="AK15" s="7"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+      <c r="Y16" s="2"/>
+      <c r="Z16" s="2"/>
+      <c r="AA16" s="2"/>
+      <c r="AB16" s="2"/>
+      <c r="AC16" s="2"/>
+      <c r="AD16" s="2"/>
+      <c r="AE16" s="2"/>
+      <c r="AF16" s="2"/>
+      <c r="AG16" s="2"/>
+      <c r="AH16" s="2"/>
+      <c r="AI16" s="2"/>
+      <c r="AJ16" s="2"/>
+      <c r="AK16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="3"/>
+      <c r="S17" s="3"/>
+      <c r="T17" s="3"/>
+      <c r="U17" s="6"/>
+      <c r="V17" s="6"/>
+      <c r="W17" s="6"/>
+      <c r="X17" s="7"/>
+      <c r="Y17" s="7"/>
+      <c r="Z17" s="7"/>
+      <c r="AA17" s="5"/>
+      <c r="AB17" s="5"/>
+      <c r="AC17" s="5"/>
+      <c r="AD17" s="10"/>
+      <c r="AE17" s="10"/>
+      <c r="AF17" s="10"/>
+      <c r="AG17" s="4"/>
+      <c r="AH17" s="4"/>
+      <c r="AI17" s="4"/>
+      <c r="AJ17" s="9"/>
+      <c r="AK17" s="9"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
+      <c r="S18" s="4"/>
+      <c r="T18" s="4"/>
+      <c r="U18" s="4"/>
+      <c r="V18" s="9"/>
+      <c r="W18" s="9"/>
+      <c r="X18" s="9"/>
+      <c r="Y18" s="3"/>
+      <c r="Z18" s="3"/>
+      <c r="AA18" s="3"/>
+      <c r="AB18" s="6"/>
+      <c r="AC18" s="6"/>
+      <c r="AD18" s="6"/>
+      <c r="AE18" s="7"/>
+      <c r="AF18" s="7"/>
+      <c r="AG18" s="7"/>
+      <c r="AH18" s="5"/>
+      <c r="AI18" s="5"/>
+      <c r="AJ18" s="5"/>
+      <c r="AK18" s="10"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="5"/>
+      <c r="U19" s="5"/>
+      <c r="V19" s="5"/>
+      <c r="W19" s="10"/>
+      <c r="X19" s="10"/>
+      <c r="Y19" s="10"/>
+      <c r="Z19" s="4"/>
+      <c r="AA19" s="4"/>
+      <c r="AB19" s="4"/>
+      <c r="AC19" s="9"/>
+      <c r="AD19" s="9"/>
+      <c r="AE19" s="9"/>
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="6"/>
+      <c r="AJ19" s="6"/>
+      <c r="AK19" s="6"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8.38"/>
+    <col customWidth="1" min="2" max="41" width="5.75"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="E1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2"/>
+      <c r="E2" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="7"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="4"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="5"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="6"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="9"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="6"/>
+      <c r="R12" s="6"/>
+      <c r="S12" s="6"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="5"/>
+      <c r="Y12" s="5"/>
+      <c r="Z12" s="4"/>
+      <c r="AA12" s="4"/>
+      <c r="AB12" s="4"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="3"/>
+      <c r="AG12" s="3"/>
+      <c r="AH12" s="3"/>
+      <c r="AI12" s="6"/>
+      <c r="AJ12" s="6"/>
+      <c r="AK12" s="6"/>
+      <c r="AL12" s="2"/>
+      <c r="AM12" s="2"/>
+      <c r="AN12" s="2"/>
+      <c r="AO12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="3"/>
+      <c r="U13" s="3"/>
+      <c r="V13" s="3"/>
+      <c r="W13" s="6"/>
+      <c r="X13" s="6"/>
+      <c r="Y13" s="6"/>
+      <c r="Z13" s="7"/>
+      <c r="AA13" s="7"/>
+      <c r="AB13" s="7"/>
+      <c r="AC13" s="5"/>
+      <c r="AD13" s="5"/>
+      <c r="AE13" s="5"/>
+      <c r="AF13" s="4"/>
+      <c r="AG13" s="4"/>
+      <c r="AH13" s="4"/>
+      <c r="AI13" s="9"/>
+      <c r="AJ13" s="9"/>
+      <c r="AK13" s="9"/>
+      <c r="AL13" s="2"/>
+      <c r="AM13" s="2"/>
+      <c r="AN13" s="2"/>
+      <c r="AO13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="4"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="9"/>
+      <c r="X14" s="9"/>
+      <c r="Y14" s="9"/>
+      <c r="Z14" s="3"/>
+      <c r="AA14" s="3"/>
+      <c r="AB14" s="3"/>
+      <c r="AC14" s="6"/>
+      <c r="AD14" s="6"/>
+      <c r="AE14" s="6"/>
+      <c r="AF14" s="7"/>
+      <c r="AG14" s="7"/>
+      <c r="AH14" s="7"/>
+      <c r="AI14" s="5"/>
+      <c r="AJ14" s="5"/>
+      <c r="AK14" s="5"/>
+      <c r="AL14" s="2"/>
+      <c r="AM14" s="2"/>
+      <c r="AN14" s="2"/>
+      <c r="AO14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
+      <c r="Z15" s="2"/>
+      <c r="AA15" s="2"/>
+      <c r="AB15" s="2"/>
+      <c r="AC15" s="2"/>
+      <c r="AD15" s="2"/>
+      <c r="AE15" s="2"/>
+      <c r="AF15" s="2"/>
+      <c r="AG15" s="2"/>
+      <c r="AH15" s="2"/>
+      <c r="AI15" s="2"/>
+      <c r="AJ15" s="2"/>
+      <c r="AK15" s="2"/>
+      <c r="AL15" s="2"/>
+      <c r="AM15" s="2"/>
+      <c r="AN15" s="2"/>
+      <c r="AO15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+      <c r="Y16" s="2"/>
+      <c r="Z16" s="2"/>
+      <c r="AA16" s="2"/>
+      <c r="AB16" s="2"/>
+      <c r="AC16" s="2"/>
+      <c r="AD16" s="2"/>
+      <c r="AE16" s="2"/>
+      <c r="AF16" s="2"/>
+      <c r="AG16" s="2"/>
+      <c r="AH16" s="2"/>
+      <c r="AI16" s="2"/>
+      <c r="AJ16" s="2"/>
+      <c r="AK16" s="2"/>
+      <c r="AL16" s="2"/>
+      <c r="AM16" s="2"/>
+      <c r="AN16" s="2"/>
+      <c r="AO16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+      <c r="S17" s="3"/>
+      <c r="T17" s="5"/>
+      <c r="U17" s="5"/>
+      <c r="V17" s="5"/>
+      <c r="W17" s="7"/>
+      <c r="X17" s="7"/>
+      <c r="Y17" s="7"/>
+      <c r="Z17" s="9"/>
+      <c r="AA17" s="9"/>
+      <c r="AB17" s="9"/>
+      <c r="AC17" s="4"/>
+      <c r="AD17" s="4"/>
+      <c r="AE17" s="4"/>
+      <c r="AF17" s="6"/>
+      <c r="AG17" s="6"/>
+      <c r="AH17" s="6"/>
+      <c r="AI17" s="3"/>
+      <c r="AJ17" s="3"/>
+      <c r="AK17" s="3"/>
+      <c r="AL17" s="2"/>
+      <c r="AM17" s="2"/>
+      <c r="AN17" s="2"/>
+      <c r="AO17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="4"/>
+      <c r="T18" s="6"/>
+      <c r="U18" s="6"/>
+      <c r="V18" s="6"/>
+      <c r="W18" s="3"/>
+      <c r="X18" s="3"/>
+      <c r="Y18" s="3"/>
+      <c r="Z18" s="5"/>
+      <c r="AA18" s="5"/>
+      <c r="AB18" s="5"/>
+      <c r="AC18" s="7"/>
+      <c r="AD18" s="7"/>
+      <c r="AE18" s="7"/>
+      <c r="AF18" s="9"/>
+      <c r="AG18" s="9"/>
+      <c r="AH18" s="9"/>
+      <c r="AI18" s="4"/>
+      <c r="AJ18" s="4"/>
+      <c r="AK18" s="4"/>
+      <c r="AL18" s="2"/>
+      <c r="AM18" s="2"/>
+      <c r="AN18" s="2"/>
+      <c r="AO18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="9"/>
+      <c r="U19" s="9"/>
+      <c r="V19" s="9"/>
+      <c r="W19" s="4"/>
+      <c r="X19" s="4"/>
+      <c r="Y19" s="4"/>
+      <c r="Z19" s="6"/>
+      <c r="AA19" s="6"/>
+      <c r="AB19" s="6"/>
+      <c r="AC19" s="3"/>
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="5"/>
+      <c r="AG19" s="5"/>
+      <c r="AH19" s="5"/>
+      <c r="AI19" s="7"/>
+      <c r="AJ19" s="7"/>
+      <c r="AK19" s="7"/>
+      <c r="AL19" s="2"/>
+      <c r="AM19" s="2"/>
+      <c r="AN19" s="2"/>
+      <c r="AO19" s="2"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8.38"/>
+    <col customWidth="1" min="2" max="41" width="5.75"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="E1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2"/>
+      <c r="E2" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="7"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="4"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="5"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="6"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="9"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6"/>
+      <c r="Q12" s="6"/>
+      <c r="R12" s="6"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="4"/>
+      <c r="W12" s="7"/>
+      <c r="X12" s="7"/>
+      <c r="Y12" s="7"/>
+      <c r="Z12" s="7"/>
+      <c r="AA12" s="6"/>
+      <c r="AB12" s="6"/>
+      <c r="AC12" s="6"/>
+      <c r="AD12" s="6"/>
+      <c r="AE12" s="4"/>
+      <c r="AF12" s="4"/>
+      <c r="AG12" s="4"/>
+      <c r="AH12" s="4"/>
+      <c r="AI12" s="7"/>
+      <c r="AJ12" s="7"/>
+      <c r="AK12" s="7"/>
+      <c r="AL12" s="2"/>
+      <c r="AM12" s="2"/>
+      <c r="AN12" s="2"/>
+      <c r="AO12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="5"/>
+      <c r="U13" s="5"/>
+      <c r="V13" s="5"/>
+      <c r="W13" s="5"/>
+      <c r="X13" s="3"/>
+      <c r="Y13" s="3"/>
+      <c r="Z13" s="3"/>
+      <c r="AA13" s="3"/>
+      <c r="AB13" s="9"/>
+      <c r="AC13" s="9"/>
+      <c r="AD13" s="9"/>
+      <c r="AE13" s="9"/>
+      <c r="AF13" s="5"/>
+      <c r="AG13" s="5"/>
+      <c r="AH13" s="5"/>
+      <c r="AI13" s="5"/>
+      <c r="AJ13" s="3"/>
+      <c r="AK13" s="3"/>
+      <c r="AL13" s="2"/>
+      <c r="AM13" s="2"/>
+      <c r="AN13" s="2"/>
+      <c r="AO13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="6"/>
+      <c r="V14" s="6"/>
+      <c r="W14" s="6"/>
+      <c r="X14" s="6"/>
+      <c r="Y14" s="4"/>
+      <c r="Z14" s="4"/>
+      <c r="AA14" s="4"/>
+      <c r="AB14" s="4"/>
+      <c r="AC14" s="7"/>
+      <c r="AD14" s="7"/>
+      <c r="AE14" s="7"/>
+      <c r="AF14" s="7"/>
+      <c r="AG14" s="6"/>
+      <c r="AH14" s="6"/>
+      <c r="AI14" s="6"/>
+      <c r="AJ14" s="6"/>
+      <c r="AK14" s="4"/>
+      <c r="AL14" s="2"/>
+      <c r="AM14" s="2"/>
+      <c r="AN14" s="2"/>
+      <c r="AO14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="3"/>
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+      <c r="U15" s="3"/>
+      <c r="V15" s="9"/>
+      <c r="W15" s="9"/>
+      <c r="X15" s="9"/>
+      <c r="Y15" s="9"/>
+      <c r="Z15" s="5"/>
+      <c r="AA15" s="5"/>
+      <c r="AB15" s="5"/>
+      <c r="AC15" s="5"/>
+      <c r="AD15" s="3"/>
+      <c r="AE15" s="3"/>
+      <c r="AF15" s="3"/>
+      <c r="AG15" s="3"/>
+      <c r="AH15" s="9"/>
+      <c r="AI15" s="9"/>
+      <c r="AJ15" s="9"/>
+      <c r="AK15" s="9"/>
+      <c r="AL15" s="2"/>
+      <c r="AM15" s="2"/>
+      <c r="AN15" s="2"/>
+      <c r="AO15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+      <c r="Y16" s="2"/>
+      <c r="Z16" s="2"/>
+      <c r="AA16" s="2"/>
+      <c r="AB16" s="2"/>
+      <c r="AC16" s="2"/>
+      <c r="AD16" s="2"/>
+      <c r="AE16" s="2"/>
+      <c r="AF16" s="2"/>
+      <c r="AG16" s="2"/>
+      <c r="AH16" s="2"/>
+      <c r="AI16" s="2"/>
+      <c r="AJ16" s="2"/>
+      <c r="AK16" s="2"/>
+      <c r="AL16" s="2"/>
+      <c r="AM16" s="2"/>
+      <c r="AN16" s="2"/>
+      <c r="AO16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="6"/>
+      <c r="T17" s="6"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="4"/>
+      <c r="X17" s="4"/>
+      <c r="Y17" s="6"/>
+      <c r="Z17" s="6"/>
+      <c r="AA17" s="7"/>
+      <c r="AB17" s="7"/>
+      <c r="AC17" s="4"/>
+      <c r="AD17" s="4"/>
+      <c r="AE17" s="6"/>
+      <c r="AF17" s="6"/>
+      <c r="AG17" s="7"/>
+      <c r="AH17" s="7"/>
+      <c r="AI17" s="4"/>
+      <c r="AJ17" s="4"/>
+      <c r="AK17" s="6"/>
+      <c r="AL17" s="2"/>
+      <c r="AM17" s="2"/>
+      <c r="AN17" s="2"/>
+      <c r="AO17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="9"/>
+      <c r="U18" s="9"/>
+      <c r="V18" s="3"/>
+      <c r="W18" s="3"/>
+      <c r="X18" s="5"/>
+      <c r="Y18" s="5"/>
+      <c r="Z18" s="9"/>
+      <c r="AA18" s="9"/>
+      <c r="AB18" s="3"/>
+      <c r="AC18" s="3"/>
+      <c r="AD18" s="5"/>
+      <c r="AE18" s="5"/>
+      <c r="AF18" s="9"/>
+      <c r="AG18" s="9"/>
+      <c r="AH18" s="3"/>
+      <c r="AI18" s="3"/>
+      <c r="AJ18" s="5"/>
+      <c r="AK18" s="5"/>
+      <c r="AL18" s="2"/>
+      <c r="AM18" s="2"/>
+      <c r="AN18" s="2"/>
+      <c r="AO18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+      <c r="Y19" s="2"/>
+      <c r="Z19" s="2"/>
+      <c r="AA19" s="2"/>
+      <c r="AB19" s="2"/>
+      <c r="AC19" s="2"/>
+      <c r="AD19" s="2"/>
+      <c r="AE19" s="2"/>
+      <c r="AF19" s="2"/>
+      <c r="AG19" s="2"/>
+      <c r="AH19" s="2"/>
+      <c r="AI19" s="2"/>
+      <c r="AJ19" s="2"/>
+      <c r="AK19" s="2"/>
+      <c r="AL19" s="2"/>
+      <c r="AM19" s="2"/>
+      <c r="AN19" s="2"/>
+      <c r="AO19" s="2"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8.38"/>
+    <col customWidth="1" min="2" max="41" width="5.75"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="E1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2"/>
+      <c r="E2" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="7"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="4"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="5"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="6"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="9"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="10"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="11"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+      <c r="S12" s="10"/>
+      <c r="T12" s="3"/>
+      <c r="U12" s="3"/>
+      <c r="V12" s="3"/>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="7"/>
+      <c r="AA12" s="7"/>
+      <c r="AB12" s="7"/>
+      <c r="AC12" s="6"/>
+      <c r="AD12" s="6"/>
+      <c r="AE12" s="6"/>
+      <c r="AF12" s="5"/>
+      <c r="AG12" s="5"/>
+      <c r="AH12" s="5"/>
+      <c r="AI12" s="11"/>
+      <c r="AJ12" s="11"/>
+      <c r="AK12" s="11"/>
+      <c r="AL12" s="2"/>
+      <c r="AM12" s="2"/>
+      <c r="AN12" s="2"/>
+      <c r="AO12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="11"/>
+      <c r="T13" s="4"/>
+      <c r="U13" s="4"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="10"/>
+      <c r="X13" s="10"/>
+      <c r="Y13" s="10"/>
+      <c r="Z13" s="3"/>
+      <c r="AA13" s="3"/>
+      <c r="AB13" s="3"/>
+      <c r="AC13" s="9"/>
+      <c r="AD13" s="9"/>
+      <c r="AE13" s="9"/>
+      <c r="AF13" s="7"/>
+      <c r="AG13" s="7"/>
+      <c r="AH13" s="7"/>
+      <c r="AI13" s="6"/>
+      <c r="AJ13" s="6"/>
+      <c r="AK13" s="6"/>
+      <c r="AL13" s="2"/>
+      <c r="AM13" s="2"/>
+      <c r="AN13" s="2"/>
+      <c r="AO13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
+      <c r="W14" s="11"/>
+      <c r="X14" s="11"/>
+      <c r="Y14" s="11"/>
+      <c r="Z14" s="4"/>
+      <c r="AA14" s="4"/>
+      <c r="AB14" s="4"/>
+      <c r="AC14" s="10"/>
+      <c r="AD14" s="10"/>
+      <c r="AE14" s="10"/>
+      <c r="AF14" s="3"/>
+      <c r="AG14" s="3"/>
+      <c r="AH14" s="3"/>
+      <c r="AI14" s="9"/>
+      <c r="AJ14" s="9"/>
+      <c r="AK14" s="9"/>
+      <c r="AL14" s="2"/>
+      <c r="AM14" s="2"/>
+      <c r="AN14" s="2"/>
+      <c r="AO14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="9"/>
+      <c r="R15" s="9"/>
+      <c r="S15" s="9"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="6"/>
+      <c r="X15" s="6"/>
+      <c r="Y15" s="6"/>
+      <c r="Z15" s="5"/>
+      <c r="AA15" s="5"/>
+      <c r="AB15" s="5"/>
+      <c r="AC15" s="11"/>
+      <c r="AD15" s="11"/>
+      <c r="AE15" s="11"/>
+      <c r="AF15" s="4"/>
+      <c r="AG15" s="4"/>
+      <c r="AH15" s="4"/>
+      <c r="AI15" s="10"/>
+      <c r="AJ15" s="10"/>
+      <c r="AK15" s="10"/>
+      <c r="AL15" s="2"/>
+      <c r="AM15" s="2"/>
+      <c r="AN15" s="2"/>
+      <c r="AO15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+      <c r="Y16" s="2"/>
+      <c r="Z16" s="2"/>
+      <c r="AA16" s="2"/>
+      <c r="AB16" s="2"/>
+      <c r="AC16" s="2"/>
+      <c r="AD16" s="2"/>
+      <c r="AE16" s="2"/>
+      <c r="AF16" s="2"/>
+      <c r="AG16" s="2"/>
+      <c r="AH16" s="2"/>
+      <c r="AI16" s="2"/>
+      <c r="AJ16" s="2"/>
+      <c r="AK16" s="2"/>
+      <c r="AL16" s="2"/>
+      <c r="AM16" s="2"/>
+      <c r="AN16" s="2"/>
+      <c r="AO16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="9"/>
+      <c r="U17" s="9"/>
+      <c r="V17" s="9"/>
+      <c r="W17" s="3"/>
+      <c r="X17" s="3"/>
+      <c r="Y17" s="3"/>
+      <c r="Z17" s="6"/>
+      <c r="AA17" s="6"/>
+      <c r="AB17" s="6"/>
+      <c r="AC17" s="7"/>
+      <c r="AD17" s="7"/>
+      <c r="AE17" s="7"/>
+      <c r="AF17" s="11"/>
+      <c r="AG17" s="11"/>
+      <c r="AH17" s="11"/>
+      <c r="AI17" s="5"/>
+      <c r="AJ17" s="5"/>
+      <c r="AK17" s="5"/>
+      <c r="AL17" s="2"/>
+      <c r="AM17" s="2"/>
+      <c r="AN17" s="2"/>
+      <c r="AO17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="11"/>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="10"/>
+      <c r="U18" s="10"/>
+      <c r="V18" s="10"/>
+      <c r="W18" s="4"/>
+      <c r="X18" s="4"/>
+      <c r="Y18" s="4"/>
+      <c r="Z18" s="9"/>
+      <c r="AA18" s="9"/>
+      <c r="AB18" s="9"/>
+      <c r="AC18" s="3"/>
+      <c r="AD18" s="3"/>
+      <c r="AE18" s="3"/>
+      <c r="AF18" s="6"/>
+      <c r="AG18" s="6"/>
+      <c r="AH18" s="6"/>
+      <c r="AI18" s="7"/>
+      <c r="AJ18" s="7"/>
+      <c r="AK18" s="7"/>
+      <c r="AL18" s="2"/>
+      <c r="AM18" s="2"/>
+      <c r="AN18" s="2"/>
+      <c r="AO18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="11"/>
+      <c r="U19" s="11"/>
+      <c r="V19" s="11"/>
+      <c r="W19" s="5"/>
+      <c r="X19" s="5"/>
+      <c r="Y19" s="5"/>
+      <c r="Z19" s="10"/>
+      <c r="AA19" s="10"/>
+      <c r="AB19" s="10"/>
+      <c r="AC19" s="4"/>
+      <c r="AD19" s="4"/>
+      <c r="AE19" s="4"/>
+      <c r="AF19" s="9"/>
+      <c r="AG19" s="9"/>
+      <c r="AH19" s="9"/>
+      <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="2"/>
+      <c r="AM19" s="2"/>
+      <c r="AN19" s="2"/>
+      <c r="AO19" s="2"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
+      <c r="T20" s="6"/>
+      <c r="U20" s="6"/>
+      <c r="V20" s="6"/>
+      <c r="W20" s="7"/>
+      <c r="X20" s="7"/>
+      <c r="Y20" s="7"/>
+      <c r="Z20" s="11"/>
+      <c r="AA20" s="11"/>
+      <c r="AB20" s="11"/>
+      <c r="AC20" s="5"/>
+      <c r="AD20" s="5"/>
+      <c r="AE20" s="5"/>
+      <c r="AF20" s="10"/>
+      <c r="AG20" s="10"/>
+      <c r="AH20" s="10"/>
+      <c r="AI20" s="4"/>
+      <c r="AJ20" s="4"/>
+      <c r="AK20" s="4"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8.38"/>
+    <col customWidth="1" min="2" max="41" width="5.75"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="E1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2"/>
+      <c r="E2" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="7"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="4"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="5"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="3"/>
+      <c r="U12" s="3"/>
+      <c r="V12" s="3"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="5"/>
+      <c r="Y12" s="5"/>
+      <c r="Z12" s="7"/>
+      <c r="AA12" s="7"/>
+      <c r="AB12" s="7"/>
+      <c r="AC12" s="4"/>
+      <c r="AD12" s="4"/>
+      <c r="AE12" s="4"/>
+      <c r="AF12" s="3"/>
+      <c r="AG12" s="3"/>
+      <c r="AH12" s="3"/>
+      <c r="AI12" s="5"/>
+      <c r="AJ12" s="5"/>
+      <c r="AK12" s="5"/>
+      <c r="AL12" s="2"/>
+      <c r="AM12" s="2"/>
+      <c r="AN12" s="2"/>
+      <c r="AO12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="4"/>
+      <c r="X13" s="4"/>
+      <c r="Y13" s="4"/>
+      <c r="Z13" s="3"/>
+      <c r="AA13" s="3"/>
+      <c r="AB13" s="3"/>
+      <c r="AC13" s="5"/>
+      <c r="AD13" s="5"/>
+      <c r="AE13" s="5"/>
+      <c r="AF13" s="7"/>
+      <c r="AG13" s="7"/>
+      <c r="AH13" s="7"/>
+      <c r="AI13" s="4"/>
+      <c r="AJ13" s="4"/>
+      <c r="AK13" s="4"/>
+      <c r="AL13" s="2"/>
+      <c r="AM13" s="2"/>
+      <c r="AN13" s="2"/>
+      <c r="AO13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
+      <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
+      <c r="Y14" s="2"/>
+      <c r="Z14" s="2"/>
+      <c r="AA14" s="2"/>
+      <c r="AB14" s="2"/>
+      <c r="AC14" s="2"/>
+      <c r="AD14" s="2"/>
+      <c r="AE14" s="2"/>
+      <c r="AF14" s="2"/>
+      <c r="AG14" s="2"/>
+      <c r="AH14" s="2"/>
+      <c r="AI14" s="2"/>
+      <c r="AJ14" s="2"/>
+      <c r="AK14" s="2"/>
+      <c r="AL14" s="2"/>
+      <c r="AM14" s="2"/>
+      <c r="AN14" s="2"/>
+      <c r="AO14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
+      <c r="Z15" s="2"/>
+      <c r="AA15" s="2"/>
+      <c r="AB15" s="2"/>
+      <c r="AC15" s="2"/>
+      <c r="AD15" s="2"/>
+      <c r="AE15" s="2"/>
+      <c r="AF15" s="2"/>
+      <c r="AG15" s="2"/>
+      <c r="AH15" s="2"/>
+      <c r="AI15" s="2"/>
+      <c r="AJ15" s="2"/>
+      <c r="AK15" s="2"/>
+      <c r="AL15" s="2"/>
+      <c r="AM15" s="2"/>
+      <c r="AN15" s="2"/>
+      <c r="AO15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="5"/>
+      <c r="U16" s="5"/>
+      <c r="V16" s="5"/>
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="4"/>
+      <c r="AA16" s="4"/>
+      <c r="AB16" s="4"/>
+      <c r="AC16" s="7"/>
+      <c r="AD16" s="7"/>
+      <c r="AE16" s="7"/>
+      <c r="AF16" s="5"/>
+      <c r="AG16" s="5"/>
+      <c r="AH16" s="5"/>
+      <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
+      <c r="AL16" s="2"/>
+      <c r="AM16" s="2"/>
+      <c r="AN16" s="2"/>
+      <c r="AO16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+      <c r="S17" s="3"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="7"/>
+      <c r="X17" s="7"/>
+      <c r="Y17" s="7"/>
+      <c r="Z17" s="5"/>
+      <c r="AA17" s="5"/>
+      <c r="AB17" s="5"/>
+      <c r="AC17" s="3"/>
+      <c r="AD17" s="3"/>
+      <c r="AE17" s="3"/>
+      <c r="AF17" s="4"/>
+      <c r="AG17" s="4"/>
+      <c r="AH17" s="4"/>
+      <c r="AI17" s="7"/>
+      <c r="AJ17" s="7"/>
+      <c r="AK17" s="7"/>
+      <c r="AL17" s="2"/>
+      <c r="AM17" s="2"/>
+      <c r="AN17" s="2"/>
+      <c r="AO17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
+      <c r="Y18" s="2"/>
+      <c r="Z18" s="2"/>
+      <c r="AA18" s="2"/>
+      <c r="AB18" s="2"/>
+      <c r="AC18" s="2"/>
+      <c r="AD18" s="2"/>
+      <c r="AE18" s="2"/>
+      <c r="AF18" s="2"/>
+      <c r="AG18" s="2"/>
+      <c r="AH18" s="2"/>
+      <c r="AI18" s="2"/>
+      <c r="AJ18" s="2"/>
+      <c r="AK18" s="2"/>
+      <c r="AL18" s="2"/>
+      <c r="AM18" s="2"/>
+      <c r="AN18" s="2"/>
+      <c r="AO18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+      <c r="Y19" s="2"/>
+      <c r="Z19" s="2"/>
+      <c r="AA19" s="2"/>
+      <c r="AB19" s="2"/>
+      <c r="AC19" s="2"/>
+      <c r="AD19" s="2"/>
+      <c r="AE19" s="2"/>
+      <c r="AF19" s="2"/>
+      <c r="AG19" s="2"/>
+      <c r="AH19" s="2"/>
+      <c r="AI19" s="2"/>
+      <c r="AJ19" s="2"/>
+      <c r="AK19" s="2"/>
+      <c r="AL19" s="2"/>
+      <c r="AM19" s="2"/>
+      <c r="AN19" s="2"/>
+      <c r="AO19" s="2"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="2"/>
+      <c r="X20" s="2"/>
+      <c r="Y20" s="2"/>
+      <c r="Z20" s="2"/>
+      <c r="AA20" s="2"/>
+      <c r="AB20" s="2"/>
+      <c r="AC20" s="2"/>
+      <c r="AD20" s="2"/>
+      <c r="AE20" s="2"/>
+      <c r="AF20" s="2"/>
+      <c r="AG20" s="2"/>
+      <c r="AH20" s="2"/>
+      <c r="AI20" s="2"/>
+      <c r="AJ20" s="2"/>
+      <c r="AK20" s="2"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="8.38"/>
+    <col customWidth="1" min="2" max="41" width="5.75"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="E1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2"/>
+      <c r="E2" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="5"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="5"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="4"/>
+      <c r="W12" s="4"/>
+      <c r="X12" s="4"/>
+      <c r="Y12" s="3"/>
+      <c r="Z12" s="3"/>
+      <c r="AA12" s="3"/>
+      <c r="AB12" s="3"/>
+      <c r="AC12" s="5"/>
+      <c r="AD12" s="5"/>
+      <c r="AE12" s="5"/>
+      <c r="AF12" s="5"/>
+      <c r="AG12" s="4"/>
+      <c r="AH12" s="4"/>
+      <c r="AI12" s="4"/>
+      <c r="AJ12" s="4"/>
+      <c r="AK12" s="3"/>
+      <c r="AL12" s="2"/>
+      <c r="AM12" s="2"/>
+      <c r="AN12" s="2"/>
+      <c r="AO12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+      <c r="U13" s="3"/>
+      <c r="V13" s="5"/>
+      <c r="W13" s="5"/>
+      <c r="X13" s="5"/>
+      <c r="Y13" s="5"/>
+      <c r="Z13" s="4"/>
+      <c r="AA13" s="4"/>
+      <c r="AB13" s="4"/>
+      <c r="AC13" s="4"/>
+      <c r="AD13" s="3"/>
+      <c r="AE13" s="3"/>
+      <c r="AF13" s="3"/>
+      <c r="AG13" s="3"/>
+      <c r="AH13" s="5"/>
+      <c r="AI13" s="5"/>
+      <c r="AJ13" s="5"/>
+      <c r="AK13" s="5"/>
+      <c r="AL13" s="2"/>
+      <c r="AM13" s="2"/>
+      <c r="AN13" s="2"/>
+      <c r="AO13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
+      <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
+      <c r="Y14" s="2"/>
+      <c r="Z14" s="2"/>
+      <c r="AA14" s="2"/>
+      <c r="AB14" s="2"/>
+      <c r="AC14" s="2"/>
+      <c r="AD14" s="2"/>
+      <c r="AE14" s="2"/>
+      <c r="AF14" s="2"/>
+      <c r="AG14" s="2"/>
+      <c r="AH14" s="2"/>
+      <c r="AI14" s="2"/>
+      <c r="AJ14" s="2"/>
+      <c r="AK14" s="2"/>
+      <c r="AL14" s="2"/>
+      <c r="AM14" s="2"/>
+      <c r="AN14" s="2"/>
+      <c r="AO14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="4"/>
+      <c r="T15" s="4"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="3"/>
+      <c r="W15" s="3"/>
+      <c r="X15" s="3"/>
+      <c r="Y15" s="4"/>
+      <c r="Z15" s="5"/>
+      <c r="AA15" s="5"/>
+      <c r="AB15" s="5"/>
+      <c r="AC15" s="3"/>
+      <c r="AD15" s="4"/>
+      <c r="AE15" s="4"/>
+      <c r="AF15" s="4"/>
+      <c r="AG15" s="5"/>
+      <c r="AH15" s="3"/>
+      <c r="AI15" s="3"/>
+      <c r="AJ15" s="3"/>
+      <c r="AK15" s="4"/>
+      <c r="AL15" s="2"/>
+      <c r="AM15" s="2"/>
+      <c r="AN15" s="2"/>
+      <c r="AO15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+      <c r="Y16" s="2"/>
+      <c r="Z16" s="2"/>
+      <c r="AA16" s="2"/>
+      <c r="AB16" s="2"/>
+      <c r="AC16" s="2"/>
+      <c r="AD16" s="2"/>
+      <c r="AE16" s="2"/>
+      <c r="AF16" s="2"/>
+      <c r="AG16" s="2"/>
+      <c r="AH16" s="2"/>
+      <c r="AI16" s="2"/>
+      <c r="AJ16" s="2"/>
+      <c r="AK16" s="2"/>
+      <c r="AL16" s="2"/>
+      <c r="AM16" s="2"/>
+      <c r="AN16" s="2"/>
+      <c r="AO16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
+      <c r="Y17" s="2"/>
+      <c r="Z17" s="2"/>
+      <c r="AA17" s="2"/>
+      <c r="AB17" s="2"/>
+      <c r="AC17" s="2"/>
+      <c r="AD17" s="2"/>
+      <c r="AE17" s="2"/>
+      <c r="AF17" s="2"/>
+      <c r="AG17" s="2"/>
+      <c r="AH17" s="2"/>
+      <c r="AI17" s="2"/>
+      <c r="AJ17" s="2"/>
+      <c r="AK17" s="2"/>
+      <c r="AL17" s="2"/>
+      <c r="AM17" s="2"/>
+      <c r="AN17" s="2"/>
+      <c r="AO17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
+      <c r="Y18" s="2"/>
+      <c r="Z18" s="2"/>
+      <c r="AA18" s="2"/>
+      <c r="AB18" s="2"/>
+      <c r="AC18" s="2"/>
+      <c r="AD18" s="2"/>
+      <c r="AE18" s="2"/>
+      <c r="AF18" s="2"/>
+      <c r="AG18" s="2"/>
+      <c r="AH18" s="2"/>
+      <c r="AI18" s="2"/>
+      <c r="AJ18" s="2"/>
+      <c r="AK18" s="2"/>
+      <c r="AL18" s="2"/>
+      <c r="AM18" s="2"/>
+      <c r="AN18" s="2"/>
+      <c r="AO18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+      <c r="Y19" s="2"/>
+      <c r="Z19" s="2"/>
+      <c r="AA19" s="2"/>
+      <c r="AB19" s="2"/>
+      <c r="AC19" s="2"/>
+      <c r="AD19" s="2"/>
+      <c r="AE19" s="2"/>
+      <c r="AF19" s="2"/>
+      <c r="AG19" s="2"/>
+      <c r="AH19" s="2"/>
+      <c r="AI19" s="2"/>
+      <c r="AJ19" s="2"/>
+      <c r="AK19" s="2"/>
+      <c r="AL19" s="2"/>
+      <c r="AM19" s="2"/>
+      <c r="AN19" s="2"/>
+      <c r="AO19" s="2"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="2"/>
+      <c r="X20" s="2"/>
+      <c r="Y20" s="2"/>
+      <c r="Z20" s="2"/>
+      <c r="AA20" s="2"/>
+      <c r="AB20" s="2"/>
+      <c r="AC20" s="2"/>
+      <c r="AD20" s="2"/>
+      <c r="AE20" s="2"/>
+      <c r="AF20" s="2"/>
+      <c r="AG20" s="2"/>
+      <c r="AH20" s="2"/>
+      <c r="AI20" s="2"/>
+      <c r="AJ20" s="2"/>
+      <c r="AK20" s="2"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>